--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0001T0006Z000C1N22_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0001T0006Z000C1N22_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>17.32409555935833</v>
+        <v>2.815165528395729</v>
       </c>
       <c r="D2" t="n">
-        <v>21.37031606288066</v>
+        <v>3.472676360218107</v>
       </c>
       <c r="E2" t="n">
-        <v>8.789053717066393</v>
+        <v>1.428221229023289</v>
       </c>
       <c r="F2" t="n">
-        <v>13.60905113446005</v>
+        <v>2.211470809349758</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>25.52763977094088</v>
+        <v>4.148241462777894</v>
       </c>
       <c r="D3" t="n">
-        <v>27.31945367265415</v>
+        <v>4.4394112218063</v>
       </c>
       <c r="E3" t="n">
-        <v>8.789053717066393</v>
+        <v>1.428221229023289</v>
       </c>
       <c r="F3" t="n">
-        <v>13.60905113446005</v>
+        <v>2.211470809349758</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.35899397360198</v>
+        <v>4.933336520710322</v>
       </c>
       <c r="D4" t="n">
-        <v>31.58689315946637</v>
+        <v>5.132870138413286</v>
       </c>
       <c r="E4" t="n">
-        <v>8.789053717066393</v>
+        <v>1.428221229023289</v>
       </c>
       <c r="F4" t="n">
-        <v>13.60905113446005</v>
+        <v>2.211470809349758</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>41.59208551519662</v>
+        <v>6.758713896219452</v>
       </c>
       <c r="D5" t="n">
-        <v>47.44494758614001</v>
+        <v>7.709803982747752</v>
       </c>
       <c r="E5" t="n">
-        <v>8.789053717066393</v>
+        <v>1.428221229023289</v>
       </c>
       <c r="F5" t="n">
-        <v>13.60905113446005</v>
+        <v>2.211470809349758</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>24.79114611180897</v>
+        <v>4.028561243168958</v>
       </c>
       <c r="D6" t="n">
-        <v>24.49074093392229</v>
+        <v>3.979745401762373</v>
       </c>
       <c r="E6" t="n">
-        <v>8.789053717066393</v>
+        <v>1.428221229023289</v>
       </c>
       <c r="F6" t="n">
-        <v>13.60905113446005</v>
+        <v>2.211470809349758</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>21.04561473446693</v>
+        <v>3.419912394350877</v>
       </c>
       <c r="D7" t="n">
-        <v>20.20270815052754</v>
+        <v>3.282940074460726</v>
       </c>
       <c r="E7" t="n">
-        <v>8.789053717066393</v>
+        <v>1.428221229023289</v>
       </c>
       <c r="F7" t="n">
-        <v>13.60905113446005</v>
+        <v>2.211470809349758</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>33.70362792950333</v>
+        <v>5.476839538544291</v>
       </c>
       <c r="D8" t="n">
-        <v>32.85955977530489</v>
+        <v>5.339678463487045</v>
       </c>
       <c r="E8" t="n">
-        <v>8.789053717066393</v>
+        <v>1.428221229023289</v>
       </c>
       <c r="F8" t="n">
-        <v>13.60905113446005</v>
+        <v>2.211470809349758</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>8.291210411997858</v>
+        <v>1.347321691949652</v>
       </c>
       <c r="D9" t="n">
-        <v>58.59733597260233</v>
+        <v>9.522067095547879</v>
       </c>
       <c r="E9" t="n">
-        <v>8.789053717066393</v>
+        <v>1.428221229023289</v>
       </c>
       <c r="F9" t="n">
-        <v>13.60905113446005</v>
+        <v>2.211470809349758</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>18.6646648027397</v>
+        <v>3.033008030445201</v>
       </c>
       <c r="D10" t="n">
-        <v>18.62007823729603</v>
+        <v>3.025762713560605</v>
       </c>
       <c r="E10" t="n">
-        <v>8.789053717066393</v>
+        <v>1.428221229023289</v>
       </c>
       <c r="F10" t="n">
-        <v>13.60905113446005</v>
+        <v>2.211470809349758</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>24.76657140148612</v>
+        <v>4.024567852741495</v>
       </c>
       <c r="D11" t="n">
-        <v>52.44544706971489</v>
+        <v>8.52238514882867</v>
       </c>
       <c r="E11" t="n">
-        <v>8.789053717066393</v>
+        <v>1.428221229023289</v>
       </c>
       <c r="F11" t="n">
-        <v>13.60905113446005</v>
+        <v>2.211470809349758</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
